--- a/template_file/HDC_result.xlsx
+++ b/template_file/HDC_result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backend\api-ppfs.test\template_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6C1CC7-CD84-49E2-9767-9BAF874E0064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8124F85-A626-4BE8-9E42-B237CFD3BF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2FCD97D8-E32F-4E5D-95CC-A4025E3D6496}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{2FCD97D8-E32F-4E5D-95CC-A4025E3D6496}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
